--- a/KONGRE_TAKIP_2.xlsx
+++ b/KONGRE_TAKIP_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yilma\Desktop\GITHUB CLONE\aslan.samsun.portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DD5938-BAC7-47D3-BB0B-A4AF5BDA8661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A89829-3FD6-4B7D-82E4-2D7B3B5697DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">KONGRE_TAKIP_2!$A$3:$AL$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -575,13 +575,13 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;₺&quot;* #,##0.00_-;\-&quot;₺&quot;* #,##0.00_-;_-&quot;₺&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ _T_L_-;\-* #,##0.00\ _T_L_-;_-* &quot;-&quot;??\ _T_L_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ _₺_-;\-* #,##0.00\ _₺_-;_-* &quot;-&quot;??\ _₺_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0\ _T_L_-;\-* #,##0\ _T_L_-;_-* &quot;-&quot;\ _T_L_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0\ &quot;TL&quot;_-;\-* #,##0\ &quot;TL&quot;_-;_-* &quot;-&quot;\ &quot;TL&quot;_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="_-* #,##0.00\ &quot;TL&quot;_-;\-* #,##0.00\ &quot;TL&quot;_-;_-* &quot;-&quot;??\ &quot;TL&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₺&quot;_-;\-* #,##0.00\ &quot;₺&quot;_-;_-* &quot;-&quot;??\ &quot;₺&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _T_L_-;\-* #,##0.00\ _T_L_-;_-* &quot;-&quot;??\ _T_L_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _₺_-;\-* #,##0.00\ _₺_-;_-* &quot;-&quot;??\ _₺_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0\ _T_L_-;\-* #,##0\ _T_L_-;_-* &quot;-&quot;\ _T_L_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0\ &quot;TL&quot;_-;\-* #,##0\ &quot;TL&quot;_-;_-* &quot;-&quot;\ &quot;TL&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ &quot;TL&quot;_-;\-* #,##0.00\ &quot;TL&quot;_-;_-* &quot;-&quot;??\ &quot;TL&quot;_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.00\ &quot;₺&quot;_-;\-* #,##0.00\ &quot;₺&quot;_-;_-* &quot;-&quot;??\ &quot;₺&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -713,7 +713,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -925,19 +925,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -949,12 +962,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
@@ -969,9 +982,9 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
@@ -999,7 +1012,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1010,7 +1023,7 @@
     <xf numFmtId="10" fontId="10" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1019,62 +1032,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1087,6 +1045,76 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1521,248 +1549,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="25" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="17" t="s">
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="19" t="s">
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" s="27"/>
-      <c r="AK1" s="27"/>
-      <c r="AL1" s="28"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="13"/>
+      <c r="AL1" s="14"/>
     </row>
     <row r="2" spans="1:38" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="31"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="17"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="17"/>
     </row>
     <row r="3" spans="1:38" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="P3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="22" t="s">
+      <c r="S3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="T3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="22" t="s">
+      <c r="U3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="22" t="s">
+      <c r="V3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="20" t="s">
+      <c r="W3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="20" t="s">
+      <c r="X3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="20" t="s">
+      <c r="Y3" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="20" t="s">
+      <c r="Z3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="AA3" s="20" t="s">
+      <c r="AA3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="AB3" s="20" t="s">
+      <c r="AB3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="17" t="s">
+      <c r="AC3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="AD3" s="17" t="s">
+      <c r="AD3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="AE3" s="17" t="s">
+      <c r="AE3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="AF3" s="17" t="s">
+      <c r="AF3" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AG3" s="17" t="s">
+      <c r="AG3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AH3" s="17" t="s">
+      <c r="AH3" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="AI3" s="19" t="s">
+      <c r="AI3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AJ3" s="19" t="s">
+      <c r="AJ3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AK3" s="19" t="s">
+      <c r="AK3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AL3" s="19" t="s">
+      <c r="AL3" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:38" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="18"/>
-      <c r="AF4" s="18"/>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="18"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="18"/>
-      <c r="AK4" s="18"/>
-      <c r="AL4" s="18"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+      <c r="AE4" s="20"/>
+      <c r="AF4" s="20"/>
+      <c r="AG4" s="20"/>
+      <c r="AH4" s="20"/>
+      <c r="AI4" s="20"/>
+      <c r="AJ4" s="20"/>
+      <c r="AK4" s="20"/>
+      <c r="AL4" s="20"/>
     </row>
     <row r="5" spans="1:38" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -1771,13 +1799,13 @@
       <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="23">
         <v>3</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="24">
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -1825,7 +1853,7 @@
       <c r="T5" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U5" s="37">
+      <c r="U5" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V5" s="4">
@@ -1843,7 +1871,7 @@
       <c r="Z5" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB5" s="4">
@@ -1861,7 +1889,7 @@
       <c r="AF5" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG5" s="37">
+      <c r="AG5" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH5" s="4">
@@ -1873,7 +1901,7 @@
       <c r="AJ5" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK5" s="37">
+      <c r="AK5" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL5" s="4">
@@ -1887,9 +1915,9 @@
       <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
@@ -1935,7 +1963,7 @@
       <c r="T6" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U6" s="37">
+      <c r="U6" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V6" s="4">
@@ -1953,7 +1981,7 @@
       <c r="Z6" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB6" s="4">
@@ -1971,7 +1999,7 @@
       <c r="AF6" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG6" s="37">
+      <c r="AG6" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH6" s="4">
@@ -1983,7 +2011,7 @@
       <c r="AJ6" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK6" s="37">
+      <c r="AK6" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL6" s="4">
@@ -1997,9 +2025,9 @@
       <c r="B7" s="5">
         <v>1</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
@@ -2045,7 +2073,7 @@
       <c r="T7" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U7" s="37">
+      <c r="U7" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V7" s="4">
@@ -2063,7 +2091,7 @@
       <c r="Z7" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB7" s="4">
@@ -2081,7 +2109,7 @@
       <c r="AF7" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG7" s="37">
+      <c r="AG7" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH7" s="4">
@@ -2093,7 +2121,7 @@
       <c r="AJ7" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK7" s="37">
+      <c r="AK7" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL7" s="4">
@@ -2107,13 +2135,13 @@
       <c r="B8" s="5">
         <v>2</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="22">
         <v>3</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="25">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -2161,7 +2189,7 @@
       <c r="T8" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U8" s="37">
+      <c r="U8" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V8" s="4">
@@ -2179,7 +2207,7 @@
       <c r="Z8" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB8" s="4">
@@ -2197,7 +2225,7 @@
       <c r="AF8" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG8" s="37">
+      <c r="AG8" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH8" s="4">
@@ -2209,7 +2237,7 @@
       <c r="AJ8" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK8" s="37">
+      <c r="AK8" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL8" s="4">
@@ -2223,9 +2251,9 @@
       <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
@@ -2271,7 +2299,7 @@
       <c r="T9" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U9" s="37">
+      <c r="U9" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V9" s="4">
@@ -2289,7 +2317,7 @@
       <c r="Z9" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB9" s="4">
@@ -2307,7 +2335,7 @@
       <c r="AF9" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG9" s="37">
+      <c r="AG9" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH9" s="4">
@@ -2319,7 +2347,7 @@
       <c r="AJ9" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK9" s="37">
+      <c r="AK9" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL9" s="4">
@@ -2333,9 +2361,9 @@
       <c r="B10" s="5">
         <v>2</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="5" t="s">
         <v>29</v>
       </c>
@@ -2381,7 +2409,7 @@
       <c r="T10" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U10" s="37">
+      <c r="U10" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V10" s="4">
@@ -2399,7 +2427,7 @@
       <c r="Z10" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB10" s="4">
@@ -2417,7 +2445,7 @@
       <c r="AF10" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG10" s="37">
+      <c r="AG10" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH10" s="4">
@@ -2429,7 +2457,7 @@
       <c r="AJ10" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK10" s="37">
+      <c r="AK10" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL10" s="4">
@@ -2497,7 +2525,7 @@
       <c r="T11" s="3">
         <v>0.30971036182762568</v>
       </c>
-      <c r="U11" s="37">
+      <c r="U11" s="10">
         <v>108.88145789343181</v>
       </c>
       <c r="V11" s="4">
@@ -2515,7 +2543,7 @@
       <c r="Z11" s="3">
         <v>0.28993672531854037</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="10">
         <v>144.66144981738486</v>
       </c>
       <c r="AB11" s="4">
@@ -2533,7 +2561,7 @@
       <c r="AF11" s="3">
         <v>1.6231854374151925E-2</v>
       </c>
-      <c r="AG11" s="37">
+      <c r="AG11" s="10">
         <v>135.12574232128509</v>
       </c>
       <c r="AH11" s="4">
@@ -2545,7 +2573,7 @@
       <c r="AJ11" s="3">
         <v>0.16310599296181522</v>
       </c>
-      <c r="AK11" s="37">
+      <c r="AK11" s="10">
         <v>123.44436021799783</v>
       </c>
       <c r="AL11" s="4">
@@ -2613,7 +2641,7 @@
       <c r="T12" s="3">
         <v>0.29007682871715412</v>
       </c>
-      <c r="U12" s="37">
+      <c r="U12" s="10">
         <v>99.757531598085876</v>
       </c>
       <c r="V12" s="4">
@@ -2631,7 +2659,7 @@
       <c r="Z12" s="3">
         <v>0.34577114427860695</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="10">
         <v>101.02006906416609</v>
       </c>
       <c r="AB12" s="4">
@@ -2649,7 +2677,7 @@
       <c r="AF12" s="3">
         <v>7.7467229323384913E-3</v>
       </c>
-      <c r="AG12" s="37">
+      <c r="AG12" s="10">
         <v>61.691496753802134</v>
       </c>
       <c r="AH12" s="4">
@@ -2661,7 +2689,7 @@
       <c r="AJ12" s="3">
         <v>0.15356126260541994</v>
       </c>
-      <c r="AK12" s="37">
+      <c r="AK12" s="10">
         <v>109.03085596079754</v>
       </c>
       <c r="AL12" s="4">
@@ -2729,7 +2757,7 @@
       <c r="T13" s="3">
         <v>0.39136944077498897</v>
       </c>
-      <c r="U13" s="37">
+      <c r="U13" s="10">
         <v>111.28235887584272</v>
       </c>
       <c r="V13" s="4">
@@ -2747,7 +2775,7 @@
       <c r="Z13" s="3">
         <v>0.24280282455187399</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="10">
         <v>106.29308673939417</v>
       </c>
       <c r="AB13" s="4">
@@ -2765,7 +2793,7 @@
       <c r="AF13" s="3">
         <v>6.0276932700235987E-3</v>
       </c>
-      <c r="AG13" s="37">
+      <c r="AG13" s="10">
         <v>97.048006733952903</v>
       </c>
       <c r="AH13" s="4">
@@ -2777,7 +2805,7 @@
       <c r="AJ13" s="3">
         <v>0.21535918626827719</v>
       </c>
-      <c r="AK13" s="37">
+      <c r="AK13" s="10">
         <v>127.08614897159801</v>
       </c>
       <c r="AL13" s="4">
@@ -2845,7 +2873,7 @@
       <c r="T14" s="3">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U14" s="37">
+      <c r="U14" s="10">
         <v>122.70053949545017</v>
       </c>
       <c r="V14" s="4">
@@ -2863,7 +2891,7 @@
       <c r="Z14" s="3">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="10">
         <v>126.44466006032084</v>
       </c>
       <c r="AB14" s="4">
@@ -2881,7 +2909,7 @@
       <c r="AF14" s="3">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG14" s="37">
+      <c r="AG14" s="10">
         <v>202.08269774392556</v>
       </c>
       <c r="AH14" s="4">
@@ -2893,7 +2921,7 @@
       <c r="AJ14" s="3">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK14" s="37">
+      <c r="AK14" s="10">
         <v>153.99774025867453</v>
       </c>
       <c r="AL14" s="4">
@@ -2961,7 +2989,7 @@
       <c r="T15" s="3">
         <v>0.22853486172166268</v>
       </c>
-      <c r="U15" s="37">
+      <c r="U15" s="10">
         <v>108.6276922684638</v>
       </c>
       <c r="V15" s="4">
@@ -2979,7 +3007,7 @@
       <c r="Z15" s="3">
         <v>0.14159671880961466</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="10">
         <v>173.01733853242206</v>
       </c>
       <c r="AB15" s="4">
@@ -2997,7 +3025,7 @@
       <c r="AF15" s="3">
         <v>2.3726771398118542E-2</v>
       </c>
-      <c r="AG15" s="37">
+      <c r="AG15" s="10">
         <v>1508.5574301086115</v>
       </c>
       <c r="AH15" s="4">
@@ -3009,7 +3037,7 @@
       <c r="AJ15" s="3">
         <v>0.12628643516366775</v>
       </c>
-      <c r="AK15" s="37">
+      <c r="AK15" s="10">
         <v>149.9991943395267</v>
       </c>
       <c r="AL15" s="4">
@@ -3077,7 +3105,7 @@
       <c r="T16" s="3">
         <v>0.22853486172166268</v>
       </c>
-      <c r="U16" s="37">
+      <c r="U16" s="10">
         <v>108.6276922684638</v>
       </c>
       <c r="V16" s="4">
@@ -3095,7 +3123,7 @@
       <c r="Z16" s="3">
         <v>0.14159671880961466</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="10">
         <v>173.01733853242206</v>
       </c>
       <c r="AB16" s="4">
@@ -3113,7 +3141,7 @@
       <c r="AF16" s="3">
         <v>2.3726771398118542E-2</v>
       </c>
-      <c r="AG16" s="37">
+      <c r="AG16" s="10">
         <v>1508.5574301086115</v>
       </c>
       <c r="AH16" s="4">
@@ -3125,7 +3153,7 @@
       <c r="AJ16" s="3">
         <v>0.12628643516366775</v>
       </c>
-      <c r="AK16" s="37">
+      <c r="AK16" s="10">
         <v>149.9991943395267</v>
       </c>
       <c r="AL16" s="4">
@@ -3193,7 +3221,7 @@
       <c r="T17" s="3">
         <v>0.30971036182762568</v>
       </c>
-      <c r="U17" s="37">
+      <c r="U17" s="10">
         <v>108.88145789343181</v>
       </c>
       <c r="V17" s="4">
@@ -3211,7 +3239,7 @@
       <c r="Z17" s="3">
         <v>0.28993672531854037</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="10">
         <v>144.66144981738486</v>
       </c>
       <c r="AB17" s="4">
@@ -3229,7 +3257,7 @@
       <c r="AF17" s="3">
         <v>1.6231854374151925E-2</v>
       </c>
-      <c r="AG17" s="37">
+      <c r="AG17" s="10">
         <v>135.12574232128509</v>
       </c>
       <c r="AH17" s="4">
@@ -3241,7 +3269,7 @@
       <c r="AJ17" s="3">
         <v>0.16310599296181522</v>
       </c>
-      <c r="AK17" s="37">
+      <c r="AK17" s="10">
         <v>123.44436021799783</v>
       </c>
       <c r="AL17" s="4">
@@ -3309,7 +3337,7 @@
       <c r="T18" s="3">
         <v>0.16252408477842004</v>
       </c>
-      <c r="U18" s="37">
+      <c r="U18" s="10">
         <v>97.744175087398446</v>
       </c>
       <c r="V18" s="4">
@@ -3327,7 +3355,7 @@
       <c r="Z18" s="3">
         <v>0.41606792945787069</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="10">
         <v>112.4728409202225</v>
       </c>
       <c r="AB18" s="4">
@@ -3345,7 +3373,7 @@
       <c r="AF18" s="3">
         <v>1.1062794005032272E-2</v>
       </c>
-      <c r="AG18" s="37">
+      <c r="AG18" s="10">
         <v>33.938656741318283</v>
       </c>
       <c r="AH18" s="4">
@@ -3357,7 +3385,7 @@
       <c r="AJ18" s="3">
         <v>0.14732391844716347</v>
       </c>
-      <c r="AK18" s="37">
+      <c r="AK18" s="10">
         <v>109.38688606201983</v>
       </c>
       <c r="AL18" s="4">
@@ -3425,7 +3453,7 @@
       <c r="T19" s="3">
         <v>7.3080337328007103E-2</v>
       </c>
-      <c r="U19" s="37">
+      <c r="U19" s="10">
         <v>124.44260837603002</v>
       </c>
       <c r="V19" s="4">
@@ -3443,7 +3471,7 @@
       <c r="Z19" s="3">
         <v>0.31246906110774986</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="10">
         <v>101.59922166557376</v>
       </c>
       <c r="AB19" s="4">
@@ -3461,7 +3489,7 @@
       <c r="AF19" s="3">
         <v>3.3073574624821162E-2</v>
       </c>
-      <c r="AG19" s="37">
+      <c r="AG19" s="10">
         <v>108.43255267780077</v>
       </c>
       <c r="AH19" s="4">
@@ -3473,7 +3501,7 @@
       <c r="AJ19" s="3">
         <v>9.263519160928127E-2</v>
       </c>
-      <c r="AK19" s="37">
+      <c r="AK19" s="10">
         <v>130.55668753046751</v>
       </c>
       <c r="AL19" s="4">
@@ -3541,7 +3569,7 @@
       <c r="T20" s="3">
         <v>0.15334389857369254</v>
       </c>
-      <c r="U20" s="37">
+      <c r="U20" s="10">
         <v>238.09612425055863</v>
       </c>
       <c r="V20" s="4">
@@ -3559,7 +3587,7 @@
       <c r="Z20" s="3">
         <v>0.16574665891923301</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="10">
         <v>142.89857109832369</v>
       </c>
       <c r="AB20" s="4">
@@ -3577,7 +3605,7 @@
       <c r="AF20" s="3">
         <v>6.5692714972056081E-3</v>
       </c>
-      <c r="AG20" s="37">
+      <c r="AG20" s="10">
         <v>77.973178705010596</v>
       </c>
       <c r="AH20" s="4">
@@ -3589,7 +3617,7 @@
       <c r="AJ20" s="3">
         <v>9.4561282728908042E-2</v>
       </c>
-      <c r="AK20" s="37">
+      <c r="AK20" s="10">
         <v>183.97608856593303</v>
       </c>
       <c r="AL20" s="4">
@@ -3657,7 +3685,7 @@
       <c r="T21" s="3">
         <v>0.27121723332468206</v>
       </c>
-      <c r="U21" s="37">
+      <c r="U21" s="10">
         <v>106.01763799839181</v>
       </c>
       <c r="V21" s="4">
@@ -3675,7 +3703,7 @@
       <c r="Z21" s="3">
         <v>0.16564592753706142</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="10">
         <v>120.9806863618895</v>
       </c>
       <c r="AB21" s="4">
@@ -3693,7 +3721,7 @@
       <c r="AF21" s="3">
         <v>2.3788567214596664E-4</v>
       </c>
-      <c r="AG21" s="37">
+      <c r="AG21" s="10">
         <v>18.996973085038359</v>
       </c>
       <c r="AH21" s="4">
@@ -3705,7 +3733,7 @@
       <c r="AJ21" s="3">
         <v>0.10757858523334816</v>
       </c>
-      <c r="AK21" s="37">
+      <c r="AK21" s="10">
         <v>133.5670099919441</v>
       </c>
       <c r="AL21" s="4">
@@ -3773,7 +3801,7 @@
       <c r="T22" s="3">
         <v>0.16252408477842004</v>
       </c>
-      <c r="U22" s="37">
+      <c r="U22" s="10">
         <v>97.744175087398446</v>
       </c>
       <c r="V22" s="4">
@@ -3791,7 +3819,7 @@
       <c r="Z22" s="3">
         <v>0.41606792945787069</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="10">
         <v>112.4728409202225</v>
       </c>
       <c r="AB22" s="4">
@@ -3809,7 +3837,7 @@
       <c r="AF22" s="3">
         <v>1.1062794005032272E-2</v>
       </c>
-      <c r="AG22" s="37">
+      <c r="AG22" s="10">
         <v>33.938656741318283</v>
       </c>
       <c r="AH22" s="4">
@@ -3821,7 +3849,7 @@
       <c r="AJ22" s="3">
         <v>0.14732391844716347</v>
       </c>
-      <c r="AK22" s="37">
+      <c r="AK22" s="10">
         <v>109.38688606201983</v>
       </c>
       <c r="AL22" s="4">
@@ -3889,7 +3917,7 @@
       <c r="T23" s="3">
         <v>0.12856584603360688</v>
       </c>
-      <c r="U23" s="37">
+      <c r="U23" s="10">
         <v>89.095935615070346</v>
       </c>
       <c r="V23" s="4">
@@ -3907,7 +3935,7 @@
       <c r="Z23" s="3">
         <v>0.18968657145595705</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="10">
         <v>118.07478116488819</v>
       </c>
       <c r="AB23" s="4">
@@ -3925,7 +3953,7 @@
       <c r="AF23" s="3">
         <v>2.0087130578123159E-2</v>
       </c>
-      <c r="AG23" s="37">
+      <c r="AG23" s="10">
         <v>42.458112047929944</v>
       </c>
       <c r="AH23" s="4">
@@ -3937,7 +3965,7 @@
       <c r="AJ23" s="3">
         <v>8.3052948468213206E-2</v>
       </c>
-      <c r="AK23" s="37">
+      <c r="AK23" s="10">
         <v>84.004080557803704</v>
       </c>
       <c r="AL23" s="4">
@@ -4005,7 +4033,7 @@
       <c r="T24" s="3">
         <v>0.37566848308199213</v>
       </c>
-      <c r="U24" s="37">
+      <c r="U24" s="10">
         <v>116.24584073760616</v>
       </c>
       <c r="V24" s="4">
@@ -4023,7 +4051,7 @@
       <c r="Z24" s="3">
         <v>0.34514734774066796</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="10">
         <v>102.33935925003479</v>
       </c>
       <c r="AB24" s="4">
@@ -4041,7 +4069,7 @@
       <c r="AF24" s="3">
         <v>6.1799622767114169E-2</v>
       </c>
-      <c r="AG24" s="37">
+      <c r="AG24" s="10">
         <v>114.65097752094931</v>
       </c>
       <c r="AH24" s="4">
@@ -4053,7 +4081,7 @@
       <c r="AJ24" s="3">
         <v>0.23941905016484005</v>
       </c>
-      <c r="AK24" s="37">
+      <c r="AK24" s="10">
         <v>129.15845180706975</v>
       </c>
       <c r="AL24" s="4">
@@ -4121,7 +4149,7 @@
       <c r="T25" s="3">
         <v>7.3080337328007103E-2</v>
       </c>
-      <c r="U25" s="37">
+      <c r="U25" s="10">
         <v>124.44260837603002</v>
       </c>
       <c r="V25" s="4">
@@ -4139,7 +4167,7 @@
       <c r="Z25" s="3">
         <v>0.31246906110774986</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="10">
         <v>101.59922166557376</v>
       </c>
       <c r="AB25" s="4">
@@ -4157,7 +4185,7 @@
       <c r="AF25" s="3">
         <v>3.3073574624821162E-2</v>
       </c>
-      <c r="AG25" s="37">
+      <c r="AG25" s="10">
         <v>108.43255267780077</v>
       </c>
       <c r="AH25" s="4">
@@ -4169,7 +4197,7 @@
       <c r="AJ25" s="3">
         <v>9.263519160928127E-2</v>
       </c>
-      <c r="AK25" s="37">
+      <c r="AK25" s="10">
         <v>130.55668753046751</v>
       </c>
       <c r="AL25" s="4">
@@ -4237,7 +4265,7 @@
       <c r="T26" s="3">
         <v>0.17944432838938792</v>
       </c>
-      <c r="U26" s="37">
+      <c r="U26" s="10">
         <v>93.238472163830494</v>
       </c>
       <c r="V26" s="4">
@@ -4255,7 +4283,7 @@
       <c r="Z26" s="3">
         <v>0.22876548142229325</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="10">
         <v>92.483822831405732</v>
       </c>
       <c r="AB26" s="4">
@@ -4273,7 +4301,7 @@
       <c r="AF26" s="3">
         <v>8.3170254403131111E-3</v>
       </c>
-      <c r="AG26" s="37">
+      <c r="AG26" s="10">
         <v>79.264612860503263</v>
       </c>
       <c r="AH26" s="4">
@@ -4285,7 +4313,7 @@
       <c r="AJ26" s="3">
         <v>0.10696460980036297</v>
       </c>
-      <c r="AK26" s="37">
+      <c r="AK26" s="10">
         <v>110.54977898583948</v>
       </c>
       <c r="AL26" s="4">
@@ -4353,7 +4381,7 @@
       <c r="T27" s="3">
         <v>0.14187319538017323</v>
       </c>
-      <c r="U27" s="37">
+      <c r="U27" s="10">
         <v>95.919897808717948</v>
       </c>
       <c r="V27" s="4">
@@ -4371,7 +4399,7 @@
       <c r="Z27" s="3">
         <v>0.26127193982220198</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="10">
         <v>108.20018679273259</v>
       </c>
       <c r="AB27" s="4">
@@ -4389,7 +4417,7 @@
       <c r="AF27" s="3">
         <v>4.8519885770007661E-2</v>
       </c>
-      <c r="AG27" s="37">
+      <c r="AG27" s="10">
         <v>80.48119700166832</v>
       </c>
       <c r="AH27" s="4">
@@ -4401,7 +4429,7 @@
       <c r="AJ27" s="3">
         <v>0.11422308069659064</v>
       </c>
-      <c r="AK27" s="37">
+      <c r="AK27" s="10">
         <v>105.72826900188991</v>
       </c>
       <c r="AL27" s="4">
@@ -4469,7 +4497,7 @@
       <c r="T28" s="3">
         <v>0.15898798976176412</v>
       </c>
-      <c r="U28" s="37">
+      <c r="U28" s="10">
         <v>102.20473392625458</v>
       </c>
       <c r="V28" s="4">
@@ -4487,7 +4515,7 @@
       <c r="Z28" s="3">
         <v>0.11589713121711084</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="10">
         <v>183.06628767819566</v>
       </c>
       <c r="AB28" s="4">
@@ -4505,7 +4533,7 @@
       <c r="AF28" s="3">
         <v>3.8397838214783819E-2</v>
       </c>
-      <c r="AG28" s="37">
+      <c r="AG28" s="10">
         <v>330.92209912551283</v>
       </c>
       <c r="AH28" s="4">
@@ -4517,7 +4545,7 @@
       <c r="AJ28" s="3">
         <v>8.8579218900291745E-2</v>
       </c>
-      <c r="AK28" s="37">
+      <c r="AK28" s="10">
         <v>114.550855571279</v>
       </c>
       <c r="AL28" s="4">
@@ -4585,7 +4613,7 @@
       <c r="T29" s="3">
         <v>0.25411830573440425</v>
       </c>
-      <c r="U29" s="37">
+      <c r="U29" s="10">
         <v>141.36629767177809</v>
       </c>
       <c r="V29" s="4">
@@ -4603,7 +4631,7 @@
       <c r="Z29" s="3">
         <v>0.40830435998881032</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="10">
         <v>105.39393655348061</v>
       </c>
       <c r="AB29" s="4">
@@ -4621,7 +4649,7 @@
       <c r="AF29" s="3">
         <v>0.10483652503698765</v>
       </c>
-      <c r="AG29" s="37">
+      <c r="AG29" s="10">
         <v>115.01393971552677</v>
       </c>
       <c r="AH29" s="4">
@@ -4633,7 +4661,7 @@
       <c r="AJ29" s="3">
         <v>0.23909561261593171</v>
       </c>
-      <c r="AK29" s="37">
+      <c r="AK29" s="10">
         <v>133.58419824375275</v>
       </c>
       <c r="AL29" s="4">
@@ -4701,7 +4729,7 @@
       <c r="T30" s="3">
         <v>0.25411830573440425</v>
       </c>
-      <c r="U30" s="37">
+      <c r="U30" s="10">
         <v>141.36629767177809</v>
       </c>
       <c r="V30" s="4">
@@ -4719,7 +4747,7 @@
       <c r="Z30" s="3">
         <v>0.40830435998881032</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="10">
         <v>105.39393655348061</v>
       </c>
       <c r="AB30" s="4">
@@ -4737,7 +4765,7 @@
       <c r="AF30" s="3">
         <v>0.10483652503698765</v>
       </c>
-      <c r="AG30" s="37">
+      <c r="AG30" s="10">
         <v>115.01393971552677</v>
       </c>
       <c r="AH30" s="4">
@@ -4749,7 +4777,7 @@
       <c r="AJ30" s="3">
         <v>0.23909561261593171</v>
       </c>
-      <c r="AK30" s="37">
+      <c r="AK30" s="10">
         <v>133.58419824375275</v>
       </c>
       <c r="AL30" s="4">
@@ -4817,7 +4845,7 @@
       <c r="T31" s="3">
         <v>0.35391935642107331</v>
       </c>
-      <c r="U31" s="37">
+      <c r="U31" s="10">
         <v>103.45397223519824</v>
       </c>
       <c r="V31" s="4">
@@ -4835,7 +4863,7 @@
       <c r="Z31" s="3">
         <v>0.23813428076888038</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="10">
         <v>111.45788273735511</v>
       </c>
       <c r="AB31" s="4">
@@ -4853,7 +4881,7 @@
       <c r="AF31" s="3">
         <v>7.4514067513457615E-3</v>
       </c>
-      <c r="AG31" s="37">
+      <c r="AG31" s="10">
         <v>21.974072214688967</v>
       </c>
       <c r="AH31" s="4">
@@ -4865,7 +4893,7 @@
       <c r="AJ31" s="3">
         <v>0.14080199191552803</v>
       </c>
-      <c r="AK31" s="37">
+      <c r="AK31" s="10">
         <v>100.26161778343048</v>
       </c>
       <c r="AL31" s="4">
@@ -4933,7 +4961,7 @@
       <c r="T32" s="3">
         <v>0.37566848308199213</v>
       </c>
-      <c r="U32" s="37">
+      <c r="U32" s="10">
         <v>116.24584073760616</v>
       </c>
       <c r="V32" s="4">
@@ -4951,7 +4979,7 @@
       <c r="Z32" s="3">
         <v>0.34514734774066796</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="10">
         <v>102.33935925003479</v>
       </c>
       <c r="AB32" s="4">
@@ -4969,7 +4997,7 @@
       <c r="AF32" s="3">
         <v>6.1799622767114169E-2</v>
       </c>
-      <c r="AG32" s="37">
+      <c r="AG32" s="10">
         <v>114.65097752094931</v>
       </c>
       <c r="AH32" s="4">
@@ -4981,7 +5009,7 @@
       <c r="AJ32" s="3">
         <v>0.23941905016484005</v>
       </c>
-      <c r="AK32" s="37">
+      <c r="AK32" s="10">
         <v>129.15845180706975</v>
       </c>
       <c r="AL32" s="4">
@@ -5049,7 +5077,7 @@
       <c r="T33" s="3">
         <v>0.25411830573440425</v>
       </c>
-      <c r="U33" s="37">
+      <c r="U33" s="10">
         <v>141.36629767177809</v>
       </c>
       <c r="V33" s="4">
@@ -5067,7 +5095,7 @@
       <c r="Z33" s="3">
         <v>0.40830435998881032</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="10">
         <v>105.39393655348061</v>
       </c>
       <c r="AB33" s="4">
@@ -5085,7 +5113,7 @@
       <c r="AF33" s="3">
         <v>0.10483652503698765</v>
       </c>
-      <c r="AG33" s="37">
+      <c r="AG33" s="10">
         <v>115.01393971552677</v>
       </c>
       <c r="AH33" s="4">
@@ -5097,7 +5125,7 @@
       <c r="AJ33" s="3">
         <v>0.23909561261593171</v>
       </c>
-      <c r="AK33" s="37">
+      <c r="AK33" s="10">
         <v>133.58419824375275</v>
       </c>
       <c r="AL33" s="4">
@@ -5165,7 +5193,7 @@
       <c r="T34" s="3">
         <v>0.15334389857369254</v>
       </c>
-      <c r="U34" s="37">
+      <c r="U34" s="10">
         <v>238.09612425055863</v>
       </c>
       <c r="V34" s="4">
@@ -5183,7 +5211,7 @@
       <c r="Z34" s="3">
         <v>0.16574665891923301</v>
       </c>
-      <c r="AA34" s="37">
+      <c r="AA34" s="10">
         <v>142.89857109832369</v>
       </c>
       <c r="AB34" s="4">
@@ -5201,7 +5229,7 @@
       <c r="AF34" s="3">
         <v>6.5692714972056081E-3</v>
       </c>
-      <c r="AG34" s="37">
+      <c r="AG34" s="10">
         <v>77.973178705010596</v>
       </c>
       <c r="AH34" s="4">
@@ -5213,7 +5241,7 @@
       <c r="AJ34" s="3">
         <v>9.4561282728908042E-2</v>
       </c>
-      <c r="AK34" s="37">
+      <c r="AK34" s="10">
         <v>183.97608856593303</v>
       </c>
       <c r="AL34" s="4">
@@ -5227,13 +5255,13 @@
       <c r="B35" s="5">
         <v>27</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="25">
         <v>3</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="25">
         <v>1</v>
       </c>
       <c r="F35" s="5" t="s">
@@ -5281,7 +5309,7 @@
       <c r="T35" s="3">
         <v>0.40365789049363093</v>
       </c>
-      <c r="U35" s="37">
+      <c r="U35" s="10">
         <v>106.86377678345136</v>
       </c>
       <c r="V35" s="4">
@@ -5299,7 +5327,7 @@
       <c r="Z35" s="3">
         <v>0.23870375010440156</v>
       </c>
-      <c r="AA35" s="37">
+      <c r="AA35" s="10">
         <v>97.966327527736595</v>
       </c>
       <c r="AB35" s="4">
@@ -5317,7 +5345,7 @@
       <c r="AF35" s="3">
         <v>5.9742507843773669E-2</v>
       </c>
-      <c r="AG35" s="37">
+      <c r="AG35" s="10">
         <v>177.81097695951885</v>
       </c>
       <c r="AH35" s="4">
@@ -5329,7 +5357,7 @@
       <c r="AJ35" s="3">
         <v>0.24454273349474767</v>
       </c>
-      <c r="AK35" s="37">
+      <c r="AK35" s="10">
         <v>114.7615674802054</v>
       </c>
       <c r="AL35" s="4">
@@ -5343,9 +5371,9 @@
       <c r="B36" s="5">
         <v>27</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="5" t="s">
         <v>29</v>
       </c>
@@ -5391,7 +5419,7 @@
       <c r="T36" s="3">
         <v>0.40365789049363093</v>
       </c>
-      <c r="U36" s="37">
+      <c r="U36" s="10">
         <v>106.86377678345136</v>
       </c>
       <c r="V36" s="4">
@@ -5409,7 +5437,7 @@
       <c r="Z36" s="3">
         <v>0.23870375010440156</v>
       </c>
-      <c r="AA36" s="37">
+      <c r="AA36" s="10">
         <v>97.966327527736595</v>
       </c>
       <c r="AB36" s="4">
@@ -5427,7 +5455,7 @@
       <c r="AF36" s="3">
         <v>5.9742507843773669E-2</v>
       </c>
-      <c r="AG36" s="37">
+      <c r="AG36" s="10">
         <v>177.81097695951885</v>
       </c>
       <c r="AH36" s="4">
@@ -5439,7 +5467,7 @@
       <c r="AJ36" s="3">
         <v>0.24454273349474767</v>
       </c>
-      <c r="AK36" s="37">
+      <c r="AK36" s="10">
         <v>114.7615674802054</v>
       </c>
       <c r="AL36" s="4">
@@ -5453,9 +5481,9 @@
       <c r="B37" s="5">
         <v>27</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
       <c r="F37" s="5" t="s">
         <v>29</v>
       </c>
@@ -5501,7 +5529,7 @@
       <c r="T37" s="3">
         <v>0.40365789049363093</v>
       </c>
-      <c r="U37" s="37">
+      <c r="U37" s="10">
         <v>106.86377678345136</v>
       </c>
       <c r="V37" s="4">
@@ -5519,7 +5547,7 @@
       <c r="Z37" s="3">
         <v>0.23870375010440156</v>
       </c>
-      <c r="AA37" s="37">
+      <c r="AA37" s="10">
         <v>97.966327527736595</v>
       </c>
       <c r="AB37" s="4">
@@ -5537,7 +5565,7 @@
       <c r="AF37" s="3">
         <v>5.9742507843773669E-2</v>
       </c>
-      <c r="AG37" s="37">
+      <c r="AG37" s="10">
         <v>177.81097695951885</v>
       </c>
       <c r="AH37" s="4">
@@ -5549,7 +5577,7 @@
       <c r="AJ37" s="3">
         <v>0.24454273349474767</v>
       </c>
-      <c r="AK37" s="37">
+      <c r="AK37" s="10">
         <v>114.7615674802054</v>
       </c>
       <c r="AL37" s="4">
@@ -5563,13 +5591,13 @@
       <c r="B38" s="5">
         <v>28</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="25">
         <v>2</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="25">
         <v>1</v>
       </c>
       <c r="F38" s="5" t="s">
@@ -5617,7 +5645,7 @@
       <c r="T38" s="3">
         <v>0.37566848308199213</v>
       </c>
-      <c r="U38" s="37">
+      <c r="U38" s="10">
         <v>116.24584073760616</v>
       </c>
       <c r="V38" s="4">
@@ -5635,7 +5663,7 @@
       <c r="Z38" s="3">
         <v>0.34514734774066796</v>
       </c>
-      <c r="AA38" s="37">
+      <c r="AA38" s="10">
         <v>102.33935925003479</v>
       </c>
       <c r="AB38" s="4">
@@ -5653,7 +5681,7 @@
       <c r="AF38" s="3">
         <v>6.1799622767114169E-2</v>
       </c>
-      <c r="AG38" s="37">
+      <c r="AG38" s="10">
         <v>114.65097752094931</v>
       </c>
       <c r="AH38" s="4">
@@ -5665,7 +5693,7 @@
       <c r="AJ38" s="3">
         <v>0.23941905016484005</v>
       </c>
-      <c r="AK38" s="37">
+      <c r="AK38" s="10">
         <v>129.15845180706975</v>
       </c>
       <c r="AL38" s="4">
@@ -5679,9 +5707,9 @@
       <c r="B39" s="5">
         <v>28</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
       <c r="F39" s="5" t="s">
         <v>29</v>
       </c>
@@ -5727,7 +5755,7 @@
       <c r="T39" s="3">
         <v>0.37566848308199213</v>
       </c>
-      <c r="U39" s="37">
+      <c r="U39" s="10">
         <v>116.24584073760616</v>
       </c>
       <c r="V39" s="4">
@@ -5745,7 +5773,7 @@
       <c r="Z39" s="3">
         <v>0.34514734774066796</v>
       </c>
-      <c r="AA39" s="37">
+      <c r="AA39" s="10">
         <v>102.33935925003479</v>
       </c>
       <c r="AB39" s="4">
@@ -5763,7 +5791,7 @@
       <c r="AF39" s="3">
         <v>6.1799622767114169E-2</v>
       </c>
-      <c r="AG39" s="37">
+      <c r="AG39" s="10">
         <v>114.65097752094931</v>
       </c>
       <c r="AH39" s="4">
@@ -5775,7 +5803,7 @@
       <c r="AJ39" s="3">
         <v>0.23941905016484005</v>
       </c>
-      <c r="AK39" s="37">
+      <c r="AK39" s="10">
         <v>129.15845180706975</v>
       </c>
       <c r="AL39" s="4">
@@ -5843,7 +5871,7 @@
       <c r="T40" s="3">
         <v>0.25097831133514625</v>
       </c>
-      <c r="U40" s="37">
+      <c r="U40" s="10">
         <v>125.23264476821257</v>
       </c>
       <c r="V40" s="4">
@@ -5861,7 +5889,7 @@
       <c r="Z40" s="3">
         <v>0.45269030877407523</v>
       </c>
-      <c r="AA40" s="37">
+      <c r="AA40" s="10">
         <v>112.39826335706753</v>
       </c>
       <c r="AB40" s="4">
@@ -5879,7 +5907,7 @@
       <c r="AF40" s="3">
         <v>4.680597014925373E-2</v>
       </c>
-      <c r="AG40" s="37">
+      <c r="AG40" s="10">
         <v>124.58753600418957</v>
       </c>
       <c r="AH40" s="4">
@@ -5891,7 +5919,7 @@
       <c r="AJ40" s="3">
         <v>0.20997991463720814</v>
       </c>
-      <c r="AK40" s="37">
+      <c r="AK40" s="10">
         <v>139.46117539848223</v>
       </c>
       <c r="AL40" s="4">
@@ -5959,7 +5987,7 @@
       <c r="T41" s="3">
         <v>0.32344994561212675</v>
       </c>
-      <c r="U41" s="37">
+      <c r="U41" s="10">
         <v>85.241489998113678</v>
       </c>
       <c r="V41" s="4">
@@ -5977,7 +6005,7 @@
       <c r="Z41" s="3">
         <v>0.34375</v>
       </c>
-      <c r="AA41" s="37">
+      <c r="AA41" s="10">
         <v>129.2984958506224</v>
       </c>
       <c r="AB41" s="4">
@@ -5995,7 +6023,7 @@
       <c r="AF41" s="3">
         <v>4.8414348843254483E-2</v>
       </c>
-      <c r="AG41" s="37">
+      <c r="AG41" s="10">
         <v>252.19321087339875</v>
       </c>
       <c r="AH41" s="4">
@@ -6007,7 +6035,7 @@
       <c r="AJ41" s="3">
         <v>0.21095436879228444</v>
       </c>
-      <c r="AK41" s="37">
+      <c r="AK41" s="10">
         <v>116.47264970476263</v>
       </c>
       <c r="AL41" s="4">
@@ -6075,7 +6103,7 @@
       <c r="T42" s="3">
         <v>0.13629494454107383</v>
       </c>
-      <c r="U42" s="37">
+      <c r="U42" s="10">
         <v>145.49348852845873</v>
       </c>
       <c r="V42" s="4">
@@ -6093,7 +6121,7 @@
       <c r="Z42" s="3">
         <v>0.14439372146832594</v>
       </c>
-      <c r="AA42" s="37">
+      <c r="AA42" s="10">
         <v>101.23333401850856</v>
       </c>
       <c r="AB42" s="4">
@@ -6111,7 +6139,7 @@
       <c r="AF42" s="3">
         <v>2.1110111513274892E-2</v>
       </c>
-      <c r="AG42" s="37">
+      <c r="AG42" s="10">
         <v>40.428955963372502</v>
       </c>
       <c r="AH42" s="4">
@@ -6123,7 +6151,7 @@
       <c r="AJ42" s="3">
         <v>8.8335165266546278E-2</v>
       </c>
-      <c r="AK42" s="37">
+      <c r="AK42" s="10">
         <v>108.24413805653879</v>
       </c>
       <c r="AL42" s="4">
@@ -6191,7 +6219,7 @@
       <c r="T43" s="3">
         <v>0.37566848308199213</v>
       </c>
-      <c r="U43" s="37">
+      <c r="U43" s="10">
         <v>116.24584073760616</v>
       </c>
       <c r="V43" s="4">
@@ -6209,7 +6237,7 @@
       <c r="Z43" s="3">
         <v>0.34514734774066796</v>
       </c>
-      <c r="AA43" s="37">
+      <c r="AA43" s="10">
         <v>102.33935925003479</v>
       </c>
       <c r="AB43" s="4">
@@ -6227,7 +6255,7 @@
       <c r="AF43" s="3">
         <v>6.1799622767114169E-2</v>
       </c>
-      <c r="AG43" s="37">
+      <c r="AG43" s="10">
         <v>114.65097752094931</v>
       </c>
       <c r="AH43" s="4">
@@ -6239,7 +6267,7 @@
       <c r="AJ43" s="3">
         <v>0.23941905016484005</v>
       </c>
-      <c r="AK43" s="37">
+      <c r="AK43" s="10">
         <v>129.15845180706975</v>
       </c>
       <c r="AL43" s="4">
@@ -6307,7 +6335,7 @@
       <c r="T44" s="3">
         <v>0.37566848308199213</v>
       </c>
-      <c r="U44" s="37">
+      <c r="U44" s="10">
         <v>116.24584073760616</v>
       </c>
       <c r="V44" s="4">
@@ -6325,7 +6353,7 @@
       <c r="Z44" s="3">
         <v>0.34514734774066796</v>
       </c>
-      <c r="AA44" s="37">
+      <c r="AA44" s="10">
         <v>102.33935925003479</v>
       </c>
       <c r="AB44" s="4">
@@ -6343,7 +6371,7 @@
       <c r="AF44" s="3">
         <v>6.1799622767114169E-2</v>
       </c>
-      <c r="AG44" s="37">
+      <c r="AG44" s="10">
         <v>114.65097752094931</v>
       </c>
       <c r="AH44" s="4">
@@ -6355,7 +6383,7 @@
       <c r="AJ44" s="3">
         <v>0.23941905016484005</v>
       </c>
-      <c r="AK44" s="37">
+      <c r="AK44" s="10">
         <v>129.15845180706975</v>
       </c>
       <c r="AL44" s="4">
@@ -6369,13 +6397,13 @@
       <c r="B45" s="5">
         <v>34</v>
       </c>
-      <c r="C45" s="21">
+      <c r="C45" s="25">
         <v>2</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="25">
         <v>1</v>
       </c>
       <c r="F45" s="5" t="s">
@@ -6423,7 +6451,7 @@
       <c r="T45" s="3">
         <v>6.6121677232788348E-2</v>
       </c>
-      <c r="U45" s="37">
+      <c r="U45" s="10">
         <v>63.193817469722589</v>
       </c>
       <c r="V45" s="4">
@@ -6441,7 +6469,7 @@
       <c r="Z45" s="3">
         <v>0.13956748097717261</v>
       </c>
-      <c r="AA45" s="37">
+      <c r="AA45" s="10">
         <v>127.43261850929977</v>
       </c>
       <c r="AB45" s="4">
@@ -6459,7 +6487,7 @@
       <c r="AF45" s="3">
         <v>2.3764105628461769E-2</v>
       </c>
-      <c r="AG45" s="37">
+      <c r="AG45" s="10">
         <v>111.99562729264865</v>
       </c>
       <c r="AH45" s="4">
@@ -6471,7 +6499,7 @@
       <c r="AJ45" s="3">
         <v>5.5192369520951669E-2</v>
       </c>
-      <c r="AK45" s="37">
+      <c r="AK45" s="10">
         <v>94.260943214180799</v>
       </c>
       <c r="AL45" s="4">
@@ -6485,9 +6513,9 @@
       <c r="B46" s="5">
         <v>34</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
       <c r="F46" s="5" t="s">
         <v>29</v>
       </c>
@@ -6533,7 +6561,7 @@
       <c r="T46" s="3">
         <v>6.6121677232788348E-2</v>
       </c>
-      <c r="U46" s="37">
+      <c r="U46" s="10">
         <v>63.193817469722589</v>
       </c>
       <c r="V46" s="4">
@@ -6551,7 +6579,7 @@
       <c r="Z46" s="3">
         <v>0.13956748097717261</v>
       </c>
-      <c r="AA46" s="37">
+      <c r="AA46" s="10">
         <v>127.43261850929977</v>
       </c>
       <c r="AB46" s="4">
@@ -6569,7 +6597,7 @@
       <c r="AF46" s="3">
         <v>2.3764105628461769E-2</v>
       </c>
-      <c r="AG46" s="37">
+      <c r="AG46" s="10">
         <v>111.99562729264865</v>
       </c>
       <c r="AH46" s="4">
@@ -6581,7 +6609,7 @@
       <c r="AJ46" s="3">
         <v>5.5192369520951669E-2</v>
       </c>
-      <c r="AK46" s="37">
+      <c r="AK46" s="10">
         <v>94.260943214180799</v>
       </c>
       <c r="AL46" s="4">
@@ -6595,13 +6623,13 @@
       <c r="B47" s="5">
         <v>35</v>
       </c>
-      <c r="C47" s="21">
+      <c r="C47" s="25">
         <v>2</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="25">
         <v>1</v>
       </c>
       <c r="F47" s="5" t="s">
@@ -6637,70 +6665,70 @@
       <c r="P47" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="Q47" s="4">
+      <c r="Q47" s="7">
         <v>7833</v>
       </c>
-      <c r="R47" s="4">
+      <c r="R47" s="7">
         <v>9468</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="8">
         <v>0.16617166617166618</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="8">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U47" s="37">
+      <c r="U47" s="11">
         <v>122.70053949545017</v>
       </c>
-      <c r="V47" s="4">
+      <c r="V47" s="7">
         <v>590803.19999999995</v>
       </c>
-      <c r="W47" s="4">
+      <c r="W47" s="7">
         <v>3001</v>
       </c>
-      <c r="X47" s="4">
+      <c r="X47" s="7">
         <v>4080</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="8">
         <v>0.21828629618853651</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="8">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA47" s="37">
+      <c r="AA47" s="11">
         <v>126.44466006032084</v>
       </c>
-      <c r="AB47" s="4">
+      <c r="AB47" s="7">
         <v>359366.39999999997</v>
       </c>
-      <c r="AC47" s="4">
+      <c r="AC47" s="7">
         <v>5387</v>
       </c>
-      <c r="AD47" s="4">
+      <c r="AD47" s="7">
         <v>7418</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="8">
         <v>5.1351712041485552E-2</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AF47" s="8">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG47" s="37">
+      <c r="AG47" s="11">
         <v>202.08269774392556</v>
       </c>
-      <c r="AH47" s="4">
+      <c r="AH47" s="7">
         <v>450198.42</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="8">
         <v>0.10771216031577349</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AJ47" s="8">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK47" s="37">
+      <c r="AK47" s="11">
         <v>153.99774025867453</v>
       </c>
-      <c r="AL47" s="4">
+      <c r="AL47" s="7">
         <v>1584829.8599999999</v>
       </c>
     </row>
@@ -6711,9 +6739,9 @@
       <c r="B48" s="6">
         <v>35</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
       <c r="F48" s="6" t="s">
         <v>29</v>
       </c>
@@ -6744,448 +6772,443 @@
       <c r="O48" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="P48" s="6" t="s">
+      <c r="P48" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="Q48" s="34">
+      <c r="Q48" s="41">
         <v>7833</v>
       </c>
-      <c r="R48" s="34">
+      <c r="R48" s="41">
         <v>9468</v>
       </c>
-      <c r="S48" s="35">
+      <c r="S48" s="42">
         <v>0.16617166617166618</v>
       </c>
-      <c r="T48" s="35">
+      <c r="T48" s="42">
         <v>0.20389353088121284</v>
       </c>
-      <c r="U48" s="38">
+      <c r="U48" s="43">
         <v>122.70053949545017</v>
       </c>
-      <c r="V48" s="34">
+      <c r="V48" s="41">
         <v>590803.19999999995</v>
       </c>
-      <c r="W48" s="34">
+      <c r="W48" s="41">
         <v>3001</v>
       </c>
-      <c r="X48" s="34">
+      <c r="X48" s="41">
         <v>4080</v>
       </c>
-      <c r="Y48" s="35">
+      <c r="Y48" s="42">
         <v>0.21828629618853651</v>
       </c>
-      <c r="Z48" s="35">
+      <c r="Z48" s="42">
         <v>0.2760113651738601</v>
       </c>
-      <c r="AA48" s="38">
+      <c r="AA48" s="43">
         <v>126.44466006032084</v>
       </c>
-      <c r="AB48" s="34">
+      <c r="AB48" s="41">
         <v>359366.39999999997</v>
       </c>
-      <c r="AC48" s="34">
+      <c r="AC48" s="41">
         <v>5387</v>
       </c>
-      <c r="AD48" s="34">
+      <c r="AD48" s="41">
         <v>7418</v>
       </c>
-      <c r="AE48" s="35">
+      <c r="AE48" s="42">
         <v>5.1351712041485552E-2</v>
       </c>
-      <c r="AF48" s="35">
+      <c r="AF48" s="42">
         <v>0.10377292503112628</v>
       </c>
-      <c r="AG48" s="38">
+      <c r="AG48" s="43">
         <v>202.08269774392556</v>
       </c>
-      <c r="AH48" s="34">
+      <c r="AH48" s="41">
         <v>450198.42</v>
       </c>
-      <c r="AI48" s="35">
+      <c r="AI48" s="42">
         <v>0.10771216031577349</v>
       </c>
-      <c r="AJ48" s="35">
+      <c r="AJ48" s="42">
         <v>0.16587429287009195</v>
       </c>
-      <c r="AK48" s="38">
+      <c r="AK48" s="43">
         <v>153.99774025867453</v>
       </c>
-      <c r="AL48" s="34">
+      <c r="AL48" s="41">
         <v>1584829.8599999999</v>
       </c>
     </row>
     <row r="49" spans="1:38" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B49" s="36">
+      <c r="B49" s="9">
         <v>36</v>
       </c>
-      <c r="C49" s="36">
-        <v>1</v>
-      </c>
-      <c r="D49" s="36" t="s">
+      <c r="C49" s="9">
+        <v>1</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E49" s="36">
-        <v>1</v>
-      </c>
-      <c r="F49" s="36" t="s">
+      <c r="E49" s="9">
+        <v>1</v>
+      </c>
+      <c r="F49" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G49" s="36" t="s">
+      <c r="G49" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H49" s="36" t="s">
+      <c r="H49" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I49" s="36" t="s">
+      <c r="I49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="36" t="s">
+      <c r="J49" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K49" s="36">
+      <c r="K49" s="9">
         <v>101</v>
       </c>
-      <c r="L49" s="36" t="s">
+      <c r="L49" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="M49" s="36" t="s">
+      <c r="M49" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N49" s="36" t="s">
+      <c r="N49" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O49" s="36" t="s">
+      <c r="O49" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="P49" s="36" t="s">
+      <c r="P49" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="Q49" s="34">
+      <c r="Q49" s="41">
         <v>2944</v>
       </c>
-      <c r="R49" s="34">
+      <c r="R49" s="41">
         <v>3293</v>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="42">
         <v>5.8726137519698393E-2</v>
       </c>
-      <c r="T49" s="35">
+      <c r="T49" s="42">
         <v>7.3080337328007103E-2</v>
       </c>
-      <c r="U49" s="38">
+      <c r="U49" s="43">
         <v>124.44260837603002</v>
       </c>
-      <c r="V49" s="34">
+      <c r="V49" s="41">
         <v>205483.19999999998</v>
       </c>
-      <c r="W49" s="34">
+      <c r="W49" s="41">
         <v>5511</v>
       </c>
-      <c r="X49" s="34">
+      <c r="X49" s="41">
         <v>5681</v>
       </c>
-      <c r="Y49" s="35">
+      <c r="Y49" s="42">
         <v>0.30755064456721914</v>
       </c>
-      <c r="Z49" s="35">
+      <c r="Z49" s="42">
         <v>0.31246906110774986</v>
       </c>
-      <c r="AA49" s="38">
+      <c r="AA49" s="43">
         <v>101.59922166557376</v>
       </c>
-      <c r="AB49" s="34">
+      <c r="AB49" s="41">
         <v>500382.48</v>
       </c>
-      <c r="AC49" s="34">
+      <c r="AC49" s="41">
         <v>3255</v>
       </c>
-      <c r="AD49" s="34">
+      <c r="AD49" s="41">
         <v>2173</v>
       </c>
-      <c r="AE49" s="35">
+      <c r="AE49" s="42">
         <v>3.0501518047902847E-2</v>
       </c>
-      <c r="AF49" s="35">
+      <c r="AF49" s="42">
         <v>3.3073574624821162E-2</v>
       </c>
-      <c r="AG49" s="38">
+      <c r="AG49" s="43">
         <v>108.43255267780077</v>
       </c>
-      <c r="AH49" s="34">
+      <c r="AH49" s="41">
         <v>131879.37</v>
       </c>
-      <c r="AI49" s="35">
+      <c r="AI49" s="42">
         <v>7.0953999646830301E-2</v>
       </c>
-      <c r="AJ49" s="35">
+      <c r="AJ49" s="42">
         <v>9.263519160928127E-2</v>
       </c>
-      <c r="AK49" s="38">
+      <c r="AK49" s="43">
         <v>130.55668753046751</v>
       </c>
-      <c r="AL49" s="34">
+      <c r="AL49" s="41">
         <v>977538.09</v>
       </c>
     </row>
     <row r="50" spans="1:38" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B50" s="36">
+      <c r="B50" s="9">
         <v>37</v>
       </c>
-      <c r="C50" s="36">
-        <v>1</v>
-      </c>
-      <c r="D50" s="36" t="s">
+      <c r="C50" s="9">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E50" s="36">
-        <v>1</v>
-      </c>
-      <c r="F50" s="36" t="s">
+      <c r="E50" s="9">
+        <v>1</v>
+      </c>
+      <c r="F50" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G50" s="36" t="s">
+      <c r="G50" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="H50" s="36" t="s">
+      <c r="H50" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I50" s="36" t="s">
+      <c r="I50" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="J50" s="36" t="s">
+      <c r="J50" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="K50" s="36">
+      <c r="K50" s="9">
         <v>226</v>
       </c>
-      <c r="L50" s="36" t="s">
+      <c r="L50" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M50" s="36" t="s">
+      <c r="M50" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N50" s="36" t="s">
+      <c r="N50" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O50" s="36" t="s">
+      <c r="O50" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P50" s="36" t="s">
+      <c r="P50" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="Q50" s="34">
+      <c r="Q50" s="41">
         <v>2996</v>
       </c>
-      <c r="R50" s="34">
+      <c r="R50" s="41">
         <v>4780</v>
       </c>
-      <c r="S50" s="35">
+      <c r="S50" s="42">
         <v>9.3677693702707773E-2</v>
       </c>
-      <c r="T50" s="35">
+      <c r="T50" s="42">
         <v>0.13629494454107383</v>
       </c>
-      <c r="U50" s="38">
+      <c r="U50" s="43">
         <v>145.49348852845873</v>
       </c>
-      <c r="V50" s="34">
+      <c r="V50" s="41">
         <v>298272</v>
       </c>
-      <c r="W50" s="34">
+      <c r="W50" s="41">
         <v>2014</v>
       </c>
-      <c r="X50" s="34">
+      <c r="X50" s="41">
         <v>2309</v>
       </c>
-      <c r="Y50" s="35">
+      <c r="Y50" s="42">
         <v>0.14263456090651558</v>
       </c>
-      <c r="Z50" s="35">
+      <c r="Z50" s="42">
         <v>0.14439372146832594</v>
       </c>
-      <c r="AA50" s="38">
+      <c r="AA50" s="43">
         <v>101.23333401850856</v>
       </c>
-      <c r="AB50" s="34">
+      <c r="AB50" s="41">
         <v>203376.72</v>
       </c>
-      <c r="AC50" s="34">
+      <c r="AC50" s="41">
         <v>3618</v>
       </c>
-      <c r="AD50" s="34">
+      <c r="AD50" s="41">
         <v>1009</v>
       </c>
-      <c r="AE50" s="35">
+      <c r="AE50" s="42">
         <v>5.2215326886996684E-2</v>
       </c>
-      <c r="AF50" s="35">
+      <c r="AF50" s="42">
         <v>2.1110111513274892E-2</v>
       </c>
-      <c r="AG50" s="38">
+      <c r="AG50" s="43">
         <v>40.428955963372502</v>
       </c>
-      <c r="AH50" s="34">
+      <c r="AH50" s="41">
         <v>61236.21</v>
       </c>
-      <c r="AI50" s="35">
+      <c r="AI50" s="42">
         <v>8.1607343226666448E-2</v>
       </c>
-      <c r="AJ50" s="35">
+      <c r="AJ50" s="42">
         <v>8.8335165266546278E-2</v>
       </c>
-      <c r="AK50" s="38">
+      <c r="AK50" s="43">
         <v>108.24413805653879</v>
       </c>
-      <c r="AL50" s="34">
+      <c r="AL50" s="41">
         <v>654557.49</v>
       </c>
     </row>
     <row r="51" spans="1:38" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B51" s="36">
+      <c r="B51" s="9">
         <v>38</v>
       </c>
-      <c r="C51" s="36">
-        <v>1</v>
-      </c>
-      <c r="D51" s="36" t="s">
+      <c r="C51" s="9">
+        <v>1</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E51" s="36">
-        <v>1</v>
-      </c>
-      <c r="F51" s="36" t="s">
+      <c r="E51" s="9">
+        <v>1</v>
+      </c>
+      <c r="F51" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G51" s="36" t="s">
+      <c r="G51" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H51" s="36" t="s">
+      <c r="H51" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="36" t="s">
+      <c r="I51" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="J51" s="36" t="s">
+      <c r="J51" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="K51" s="36">
+      <c r="K51" s="9">
         <v>167</v>
       </c>
-      <c r="L51" s="36" t="s">
+      <c r="L51" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="M51" s="36" t="s">
+      <c r="M51" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N51" s="36" t="s">
+      <c r="N51" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O51" s="36" t="s">
+      <c r="O51" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P51" s="36" t="s">
+      <c r="P51" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="Q51" s="34">
+      <c r="Q51" s="41">
         <v>13133</v>
       </c>
-      <c r="R51" s="34">
+      <c r="R51" s="41">
         <v>14430</v>
       </c>
-      <c r="S51" s="35">
+      <c r="S51" s="42">
         <v>0.34210320664773763</v>
       </c>
-      <c r="T51" s="35">
+      <c r="T51" s="42">
         <v>0.35391935642107331</v>
       </c>
-      <c r="U51" s="38">
+      <c r="U51" s="43">
         <v>103.45397223519824</v>
       </c>
-      <c r="V51" s="34">
+      <c r="V51" s="41">
         <v>900432</v>
       </c>
-      <c r="W51" s="34">
+      <c r="W51" s="41">
         <v>2416</v>
       </c>
-      <c r="X51" s="34">
+      <c r="X51" s="41">
         <v>2614</v>
       </c>
-      <c r="Y51" s="35">
+      <c r="Y51" s="42">
         <v>0.21365405022992573</v>
       </c>
-      <c r="Z51" s="35">
+      <c r="Z51" s="42">
         <v>0.23813428076888038</v>
       </c>
-      <c r="AA51" s="38">
+      <c r="AA51" s="43">
         <v>111.45788273735511</v>
       </c>
-      <c r="AB51" s="34">
+      <c r="AB51" s="41">
         <v>230241.12</v>
       </c>
-      <c r="AC51" s="34">
+      <c r="AC51" s="41">
         <v>2950</v>
       </c>
-      <c r="AD51" s="34">
+      <c r="AD51" s="41">
         <v>562</v>
       </c>
-      <c r="AE51" s="35">
+      <c r="AE51" s="42">
         <v>3.3909994827288924E-2</v>
       </c>
-      <c r="AF51" s="35">
+      <c r="AF51" s="42">
         <v>7.4514067513457615E-3</v>
       </c>
-      <c r="AG51" s="38">
+      <c r="AG51" s="43">
         <v>21.974072214688967</v>
       </c>
-      <c r="AH51" s="34">
+      <c r="AH51" s="41">
         <v>34107.78</v>
       </c>
-      <c r="AI51" s="35">
+      <c r="AI51" s="42">
         <v>0.14043459005385944</v>
       </c>
-      <c r="AJ51" s="35">
+      <c r="AJ51" s="42">
         <v>0.14080199191552803</v>
       </c>
-      <c r="AK51" s="38">
+      <c r="AK51" s="43">
         <v>100.26161778343048</v>
       </c>
-      <c r="AL51" s="34">
+      <c r="AL51" s="41">
         <v>1237469.2200000002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="AI1:AL2"/>
-    <mergeCell ref="W1:AB2"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q1:V2"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="AC1:AH2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D35:D37"/>
     <mergeCell ref="A3:A4"/>
@@ -7202,29 +7225,34 @@
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D38:D39"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="AI1:AL2"/>
+    <mergeCell ref="W1:AB2"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="Q1:V2"/>
+    <mergeCell ref="AC1:AH2"/>
     <mergeCell ref="AC3:AC4"/>
     <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="X3:X4"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AH3:AH4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A1:P2"/>
-    <mergeCell ref="N3:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
